--- a/data/9_месяцев_2026.xlsx
+++ b/data/9_месяцев_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s.kulikova\Desktop\Аналитика сент\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FA93BF-E662-40EA-BC0E-F3B9A1442FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7295E0FA-04EE-45C4-81B7-5B53FC79233F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13224" uniqueCount="2412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13229" uniqueCount="2412">
   <si>
     <t>№ п/п</t>
   </si>
@@ -54023,9 +54023,11 @@
         <v>37</v>
       </c>
       <c r="L913" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="M913" s="5"/>
+        <v>2408</v>
+      </c>
+      <c r="M913" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="N913" s="14" t="s">
         <v>80</v>
       </c>
@@ -54077,9 +54079,11 @@
         <v>37</v>
       </c>
       <c r="L914" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="M914" s="5"/>
+        <v>2408</v>
+      </c>
+      <c r="M914" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="N914" s="14" t="s">
         <v>80</v>
       </c>
@@ -54131,9 +54135,11 @@
         <v>37</v>
       </c>
       <c r="L915" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="M915" s="5"/>
+        <v>2408</v>
+      </c>
+      <c r="M915" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="N915" s="14" t="s">
         <v>80</v>
       </c>
@@ -54185,9 +54191,11 @@
         <v>37</v>
       </c>
       <c r="L916" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="M916" s="5"/>
+        <v>2408</v>
+      </c>
+      <c r="M916" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="N916" s="14" t="s">
         <v>80</v>
       </c>
@@ -54293,9 +54301,11 @@
         <v>37</v>
       </c>
       <c r="L918" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="M918" s="5"/>
+        <v>2408</v>
+      </c>
+      <c r="M918" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="N918" s="14" t="s">
         <v>59</v>
       </c>
@@ -58117,7 +58127,7 @@
         <v>37</v>
       </c>
       <c r="L990" s="5" t="s">
-        <v>77</v>
+        <v>2408</v>
       </c>
       <c r="M990" s="5" t="s">
         <v>27</v>
